--- a/data/restructuring_event_calendar_2026.xlsx
+++ b/data/restructuring_event_calendar_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://haselhorstassociates.sharepoint.com/sites/AIRoadmap/Freigegebene Dokumente/Main/05_AI_Workflows_Claude/05_Event_Calendar_Sync/03_Input/01_Demo_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_5EF903D8CD2F786585A40DBA8A139FB0F10F9997" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9434B57-6EA1-AC49-9698-8BB8A54D1913}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_5EF903D8CD2F786585A40DBA8A139FB0F10F9997" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D1C2A71-014B-E44E-9B05-7129862486D3}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1004,7 +1004,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1027,15 +1027,108 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB4B4B4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1138,11 +1231,514 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E79"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFB4B4B4"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4B4B4"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4B4B4"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4B4B4"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4B4B4"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF0563C1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4B4B4"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4B4B4"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4B4B4"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4B4B4"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4B4B4"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4B4B4"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4B4B4"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4B4B4"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4B4B4"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4B4B4"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFB4B4B4"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4B4B4"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFB4B4B4"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFB4B4B4"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFB4B4B4"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFB4B4B4"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFB4B4B4"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1153,6 +1749,24 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9F5606C0-B04B-7940-9045-EA59823B38D0}" name="Tabelle1" displayName="Tabelle1" ref="A4:I73" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
+  <autoFilter ref="A4:I73" xr:uid="{9F5606C0-B04B-7940-9045-EA59823B38D0}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{9B4BE18E-9ECF-344B-AA35-6463C77D52B1}" name="Date" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{7F4D1786-F9B2-9A4A-B0FB-5301665D35AB}" name="Event" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{B27E43CE-F970-9A46-9B13-47D78B7F242D}" name="Organiser" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{53A979FA-13A0-CC4E-975F-6A2B14909A45}" name="Location" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{9B18A7F6-6292-644F-8C75-D4F73C39F7DB}" name="Country" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{21137C13-BFD4-C741-81A3-9E6204546E76}" name="Cost" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{CADE733B-602D-734E-967F-489CF042769C}" name="Link" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{C11F80C6-3FDA-4548-9948-44DAACFC7FB2}" name="Status" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{F7C47F9E-7F6E-694E-BC2D-AEDCE180976C}" name="Category" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1447,7 +2061,7 @@
     <col min="2" max="2" width="52" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="45" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
@@ -1455,2113 +2069,2112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="31" t="s">
+      <c r="K4" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="41" t="s">
         <v>290</v>
       </c>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
     </row>
     <row r="5" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="32" t="s">
+      <c r="K5" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="L5" s="33" t="s">
+      <c r="L5" s="32" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="34" t="s">
+      <c r="K6" s="33" t="s">
         <v>284</v>
       </c>
-      <c r="L6" s="33" t="s">
+      <c r="L6" s="32" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="35" t="s">
+      <c r="K7" s="34" t="s">
         <v>284</v>
       </c>
-      <c r="L7" s="33" t="s">
+      <c r="L7" s="32" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="36" t="s">
+      <c r="K8" s="35" t="s">
         <v>284</v>
       </c>
-      <c r="L8" s="33" t="s">
+      <c r="L8" s="32" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="36" t="s">
         <v>284</v>
       </c>
-      <c r="L9" s="33" t="s">
+      <c r="L9" s="32" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="44" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="38" t="s">
+      <c r="K10" s="37" t="s">
         <v>284</v>
       </c>
-      <c r="L10" s="33" t="s">
+      <c r="L10" s="32" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="51" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" s="8" t="s">
+      <c r="H12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" s="52" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I13" s="8" t="s">
+      <c r="H13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="52" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" s="8" t="s">
+      <c r="H14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="52" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I15" s="8" t="s">
+      <c r="H15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="52" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I16" s="8" t="s">
+      <c r="H16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="52" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I17" s="8" t="s">
+      <c r="H17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="52" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="8" t="s">
+      <c r="H18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="52" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="18" t="s">
+      <c r="G19" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="17" t="s">
+      <c r="H19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="53" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="G20" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H20" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I20" s="17" t="s">
+      <c r="H20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" s="53" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="H21" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="13" t="s">
+      <c r="H21" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H22" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I22" s="17" t="s">
+      <c r="H22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="53" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="17" t="s">
+      <c r="H23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I24" s="17" t="s">
+      <c r="H24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" s="53" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="H25" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I25" s="13" t="s">
+      <c r="H25" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H26" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I26" s="17" t="s">
+      <c r="H26" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I26" s="53" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="H27" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I27" s="17" t="s">
+      <c r="H27" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I27" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H28" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I28" s="17" t="s">
+      <c r="H28" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I28" s="53" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="G29" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="H29" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I29" s="13" t="s">
+      <c r="H29" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I29" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="G30" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="H30" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I30" s="13" t="s">
+      <c r="H30" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I30" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="H31" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I31" s="13" t="s">
+      <c r="H31" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="H32" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I32" s="17" t="s">
+      <c r="H32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I32" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G33" s="18" t="s">
+      <c r="G33" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="H33" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I33" s="17" t="s">
+      <c r="H33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I33" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="18" t="s">
+      <c r="G34" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H34" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I34" s="17" t="s">
+      <c r="H34" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I34" s="53" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G35" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="H35" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I35" s="17" t="s">
+      <c r="H35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I35" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G36" s="14" t="s">
+      <c r="G36" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="H36" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I36" s="13" t="s">
+      <c r="H36" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I36" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="E37" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G37" s="18" t="s">
+      <c r="G37" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="H37" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I37" s="17" t="s">
+      <c r="H37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I37" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E38" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G38" s="18" t="s">
+      <c r="G38" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="H38" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I38" s="17" t="s">
+      <c r="H38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I38" s="53" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H39" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I39" s="17" t="s">
+      <c r="H39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I39" s="53" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G40" s="14" t="s">
+      <c r="G40" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="H40" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I40" s="13" t="s">
+      <c r="H40" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I40" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="46" t="s">
         <v>169</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="H41" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I41" s="17" t="s">
+      <c r="H41" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I41" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G42" s="18" t="s">
+      <c r="G42" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="H42" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I42" s="17" t="s">
+      <c r="H42" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I42" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="47" t="s">
         <v>179</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F43" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="H43" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I43" s="13" t="s">
+      <c r="H43" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I43" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F44" s="21" t="s">
+      <c r="F44" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="G44" s="22" t="s">
+      <c r="G44" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="H44" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I44" s="21" t="s">
+      <c r="H44" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I44" s="55" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19" t="s">
+      <c r="A45" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C45" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="F45" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="G45" s="22" t="s">
+      <c r="G45" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H45" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I45" s="21" t="s">
+      <c r="H45" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I45" s="55" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="19" t="s">
+      <c r="A46" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="21" t="s">
+      <c r="F46" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="G46" s="22" t="s">
+      <c r="G46" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="H46" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I46" s="21" t="s">
+      <c r="H46" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I46" s="55" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E47" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F47" s="13" t="s">
+      <c r="F47" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="H47" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I47" s="13" t="s">
+      <c r="H47" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I47" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="19" t="s">
+      <c r="A48" s="48" t="s">
         <v>199</v>
       </c>
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="21" t="s">
+      <c r="F48" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="G48" s="22" t="s">
+      <c r="G48" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="H48" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I48" s="21" t="s">
+      <c r="H48" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="I48" s="55" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="47" t="s">
         <v>203</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F49" s="13" t="s">
+      <c r="F49" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="G49" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="H49" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I49" s="13" t="s">
+      <c r="H49" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I49" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="47" t="s">
         <v>207</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="F50" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="G50" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="H50" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I50" s="13" t="s">
+      <c r="H50" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I50" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="49" t="s">
         <v>212</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="22" t="s">
         <v>213</v>
       </c>
-      <c r="C51" s="23" t="s">
+      <c r="C51" s="22" t="s">
         <v>176</v>
       </c>
-      <c r="D51" s="23" t="s">
+      <c r="D51" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="E51" s="24" t="s">
+      <c r="E51" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="F51" s="25" t="s">
+      <c r="F51" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G51" s="26" t="s">
+      <c r="G51" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="H51" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I51" s="25" t="s">
+      <c r="H51" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I51" s="56" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="B52" s="23" t="s">
+      <c r="B52" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="D52" s="23" t="s">
+      <c r="D52" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="E52" s="24" t="s">
+      <c r="E52" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F52" s="25" t="s">
+      <c r="F52" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G52" s="26" t="s">
+      <c r="G52" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="H52" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I52" s="25" t="s">
+      <c r="H52" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I52" s="56" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="22" t="s">
         <v>220</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="D53" s="23" t="s">
+      <c r="D53" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="E53" s="24" t="s">
+      <c r="E53" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F53" s="25" t="s">
+      <c r="F53" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="G53" s="26" t="s">
+      <c r="G53" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="H53" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I53" s="25" t="s">
+      <c r="H53" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I53" s="56" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="D54" s="23" t="s">
+      <c r="D54" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="E54" s="24" t="s">
+      <c r="E54" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="25" t="s">
+      <c r="F54" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G54" s="26" t="s">
+      <c r="G54" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="H54" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I54" s="25" t="s">
+      <c r="H54" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I54" s="56" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="47" t="s">
         <v>227</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="E55" s="12" t="s">
+      <c r="E55" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F55" s="13" t="s">
+      <c r="F55" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G55" s="14" t="s">
+      <c r="G55" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="H55" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I55" s="13" t="s">
+      <c r="H55" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I55" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="49" t="s">
         <v>229</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="B56" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D56" s="23" t="s">
+      <c r="D56" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="E56" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F56" s="25" t="s">
+      <c r="F56" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G56" s="26" t="s">
+      <c r="G56" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="H56" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I56" s="25" t="s">
+      <c r="H56" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I56" s="56" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="B57" s="23" t="s">
+      <c r="B57" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D57" s="23" t="s">
+      <c r="D57" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="E57" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F57" s="25" t="s">
+      <c r="F57" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="G57" s="26" t="s">
+      <c r="G57" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="H57" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I57" s="25" t="s">
+      <c r="H57" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I57" s="56" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="49" t="s">
         <v>234</v>
       </c>
-      <c r="B58" s="23" t="s">
+      <c r="B58" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="D58" s="23" t="s">
+      <c r="D58" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="E58" s="24" t="s">
+      <c r="E58" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F58" s="25" t="s">
+      <c r="F58" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G58" s="26" t="s">
+      <c r="G58" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="H58" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I58" s="25" t="s">
+      <c r="H58" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I58" s="56" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="46" t="s">
         <v>238</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="D59" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E59" s="16" t="s">
+      <c r="E59" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F59" s="17" t="s">
+      <c r="F59" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G59" s="18" t="s">
+      <c r="G59" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="H59" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I59" s="17" t="s">
+      <c r="H59" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I59" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="49" t="s">
         <v>242</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="B60" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="22" t="s">
         <v>244</v>
       </c>
-      <c r="D60" s="23" t="s">
+      <c r="D60" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="E60" s="24" t="s">
+      <c r="E60" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F60" s="25" t="s">
+      <c r="F60" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G60" s="26" t="s">
+      <c r="G60" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="H60" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I60" s="25" t="s">
+      <c r="H60" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I60" s="56" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="B61" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="D61" s="23" t="s">
+      <c r="D61" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="E61" s="24" t="s">
+      <c r="E61" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F61" s="25" t="s">
+      <c r="F61" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="G61" s="26" t="s">
+      <c r="G61" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="H61" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I61" s="25" t="s">
+      <c r="H61" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I61" s="56" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="D62" s="23" t="s">
+      <c r="D62" s="22" t="s">
         <v>250</v>
       </c>
-      <c r="E62" s="24" t="s">
+      <c r="E62" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F62" s="25" t="s">
+      <c r="F62" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="G62" s="26" t="s">
+      <c r="G62" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H62" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I62" s="25" t="s">
+      <c r="H62" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I62" s="56" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="23" t="s">
+      <c r="A63" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="B63" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="D63" s="23" t="s">
+      <c r="D63" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="E63" s="24" t="s">
+      <c r="E63" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="F63" s="25" t="s">
+      <c r="F63" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="G63" s="26" t="s">
+      <c r="G63" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="H63" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I63" s="25" t="s">
+      <c r="H63" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I63" s="56" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="B64" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D64" s="23" t="s">
+      <c r="D64" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="E64" s="24" t="s">
+      <c r="E64" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="F64" s="25" t="s">
+      <c r="F64" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="G64" s="26" t="s">
+      <c r="G64" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="H64" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I64" s="25" t="s">
+      <c r="H64" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I64" s="56" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="23" t="s">
+      <c r="A65" s="49" t="s">
         <v>254</v>
       </c>
-      <c r="B65" s="23" t="s">
+      <c r="B65" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="D65" s="23" t="s">
+      <c r="D65" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="F65" s="25" t="s">
+      <c r="F65" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G65" s="26" t="s">
+      <c r="G65" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="H65" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="I65" s="25" t="s">
+      <c r="H65" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I65" s="56" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="47" t="s">
         <v>254</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F66" s="13" t="s">
+      <c r="F66" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G66" s="14" t="s">
+      <c r="G66" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="H66" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="I66" s="13" t="s">
+      <c r="H66" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I66" s="54" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="27" t="s">
+      <c r="A67" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="B67" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="C67" s="27" t="s">
+      <c r="C67" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D67" s="27" t="s">
+      <c r="D67" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="E67" s="28" t="s">
+      <c r="E67" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F67" s="29" t="s">
+      <c r="F67" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G67" s="30" t="s">
+      <c r="G67" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="H67" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I67" s="29" t="s">
+      <c r="H67" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I67" s="57" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="27" t="s">
+      <c r="A68" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="B68" s="27" t="s">
+      <c r="B68" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="C68" s="27" t="s">
+      <c r="C68" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D68" s="27" t="s">
+      <c r="D68" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="E68" s="28" t="s">
+      <c r="E68" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F68" s="29" t="s">
+      <c r="F68" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G68" s="30" t="s">
+      <c r="G68" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="H68" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I68" s="29" t="s">
+      <c r="H68" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I68" s="57" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="27" t="s">
+      <c r="A69" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="B69" s="27" t="s">
+      <c r="B69" s="26" t="s">
         <v>266</v>
       </c>
-      <c r="C69" s="27" t="s">
+      <c r="C69" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D69" s="27" t="s">
+      <c r="D69" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="E69" s="28" t="s">
+      <c r="E69" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F69" s="29" t="s">
+      <c r="F69" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G69" s="30" t="s">
+      <c r="G69" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="H69" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I69" s="29" t="s">
+      <c r="H69" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I69" s="57" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="27" t="s">
+      <c r="A70" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="C70" s="27" t="s">
+      <c r="C70" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D70" s="27" t="s">
+      <c r="D70" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="E70" s="28" t="s">
+      <c r="E70" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="F70" s="29" t="s">
+      <c r="F70" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="G70" s="30" t="s">
+      <c r="G70" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="H70" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I70" s="29" t="s">
+      <c r="H70" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I70" s="57" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="27" t="s">
+      <c r="A71" s="50" t="s">
         <v>269</v>
       </c>
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="C71" s="27" t="s">
+      <c r="C71" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="D71" s="27" t="s">
+      <c r="D71" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="E71" s="28" t="s">
+      <c r="E71" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F71" s="29" t="s">
+      <c r="F71" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="G71" s="30" t="s">
+      <c r="G71" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="H71" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I71" s="29" t="s">
+      <c r="H71" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I71" s="57" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="27" t="s">
+      <c r="A72" s="50" t="s">
         <v>269</v>
       </c>
-      <c r="B72" s="27" t="s">
+      <c r="B72" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="C72" s="27" t="s">
+      <c r="C72" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="D72" s="27" t="s">
+      <c r="D72" s="26" t="s">
         <v>277</v>
       </c>
-      <c r="E72" s="28" t="s">
+      <c r="E72" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F72" s="29" t="s">
+      <c r="F72" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="G72" s="30" t="s">
+      <c r="G72" s="29" t="s">
         <v>278</v>
       </c>
-      <c r="H72" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I72" s="29" t="s">
+      <c r="H72" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="I72" s="57" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="27" t="s">
+      <c r="A73" s="61" t="s">
         <v>269</v>
       </c>
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="62" t="s">
         <v>279</v>
       </c>
-      <c r="C73" s="27" t="s">
+      <c r="C73" s="62" t="s">
         <v>280</v>
       </c>
-      <c r="D73" s="27" t="s">
+      <c r="D73" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="E73" s="28" t="s">
+      <c r="E73" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="F73" s="29" t="s">
+      <c r="F73" s="64" t="s">
         <v>273</v>
       </c>
-      <c r="G73" s="30" t="s">
+      <c r="G73" s="65" t="s">
         <v>282</v>
       </c>
-      <c r="H73" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="I73" s="29" t="s">
+      <c r="H73" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="I73" s="66" t="s">
         <v>89</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I73" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M4:U4"/>
@@ -3639,10 +4252,33 @@
     <hyperlink ref="G73" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId70"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="239df7f2-98c0-4b21-bce8-bfddaf72a22d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b541a2e5-6919-4c18-819d-6f9beb94c080">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D64F4D755BE2E349AF8B57C761DE3BFA" ma:contentTypeVersion="10" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7c372a3e51f366a63ca64bb29072728e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b541a2e5-6919-4c18-819d-6f9beb94c080" xmlns:ns3="239df7f2-98c0-4b21-bce8-bfddaf72a22d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="40f1e2ce5c9d8c089f89cb07a6218374" ns2:_="" ns3:_="">
     <xsd:import namespace="b541a2e5-6919-4c18-819d-6f9beb94c080"/>
@@ -3831,27 +4467,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="239df7f2-98c0-4b21-bce8-bfddaf72a22d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b541a2e5-6919-4c18-819d-6f9beb94c080">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79796166-5335-40B8-AD37-15C8A8E97BF3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F00F86F-3590-4D0E-B5CD-8C8C7F7B5DBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="239df7f2-98c0-4b21-bce8-bfddaf72a22d"/>
+    <ds:schemaRef ds:uri="b541a2e5-6919-4c18-819d-6f9beb94c080"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F120126-951F-4771-8062-3BD755774F5A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3868,29 +4509,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F00F86F-3590-4D0E-B5CD-8C8C7F7B5DBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="b541a2e5-6919-4c18-819d-6f9beb94c080"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="239df7f2-98c0-4b21-bce8-bfddaf72a22d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79796166-5335-40B8-AD37-15C8A8E97BF3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>